--- a/output/2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx
@@ -484,10 +484,9 @@
           <t>+385 22 646 168 / +385 22 646 179 / +385 91 457 9915</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro Kärcher gestito da N K &amp; M d.o.o. (rete confermata anche su nkim.hr); vendita e assistenza aspiratori industriali/professionali Kärcher e macchine per pulizia professionale. Esistenza confermata tramite sito ufficiale Kärcher e articoli locali (dalmatinskiportal.hr, sibenik.in).</t>
+          <t>Centro Kärcher gestito da N K &amp; M d.o.o. (rete confermata anche su nkim.hr); vendita e assistenza aspiratori industriali/professionali Kärcher e macchine per pulizia professionale. Esistenza confermata tramite sito ufficiale Kärcher e articoli locali (dalmatinskiportal.hr, sibenik.in). [DUPLICATO — vedi anche: 2026-09-19_20_Croazia_Sibensko-kninska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -732,7 +731,6 @@
           <t>022 247 090</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Punto vendita locale di catena nazionale di ferramenta/bricolage con reparto aspiratori industriali classe M/L e attrezzature da cantiere, venduti anche a professionisti/artigiani. Non è un distributore B2B specializzato ma un canale retail generalista con vendita anche a imprese; eventuale accordo di distribuzione andrebbe valutato a livello di sede centrale Pevex piuttosto che sul singolo punto vendita. Esistenza e recapito confermati (sito ufficiale, Google Maps, mojkatalog.hr).</t>

--- a/output/2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Punto vendita locale di catena nazionale di ferramenta/bricolage con reparto aspiratori industriali classe M/L e attrezzature da cantiere, venduti anche a professionisti/artigiani. Non è un distributore B2B specializzato ma un canale retail generalista con vendita anche a imprese; eventuale accordo di distribuzione andrebbe valutato a livello di sede centrale Pevex piuttosto che sul singolo punto vendita. Esistenza e recapito confermati (sito ufficiale, Google Maps, mojkatalog.hr).</t>
+          <t>Punto vendita locale di catena nazionale di ferramenta/bricolage con reparto aspiratori industriali classe M/L e attrezzature da cantiere, venduti anche a professionisti/artigiani. Non è un distributore B2B specializzato ma un canale retail generalista con vendita anche a imprese; eventuale accordo di distribuzione andrebbe valutato a livello di sede centrale Pevex piuttosto che sul singolo punto vendita. Esistenza e recapito confermati (sito ufficiale, Google Maps, mojkatalog.hr). [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
